--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.7851464506105</v>
+        <v>5.165086298224206</v>
       </c>
       <c r="D2" t="n">
-        <v>32.25841300516273</v>
+        <v>5.241992113338944</v>
       </c>
       <c r="E2" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F2" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.24124033131548</v>
+        <v>4.751701553838766</v>
       </c>
       <c r="D3" t="n">
-        <v>29.42558131242691</v>
+        <v>4.781656963269374</v>
       </c>
       <c r="E3" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F3" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>16.61353100050879</v>
+        <v>2.699698787582679</v>
       </c>
       <c r="D4" t="n">
-        <v>17.31066599040039</v>
+        <v>2.812983223440063</v>
       </c>
       <c r="E4" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F4" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>47.12412716388479</v>
+        <v>7.657670664131279</v>
       </c>
       <c r="D5" t="n">
-        <v>25.66870095865757</v>
+        <v>4.171163905781855</v>
       </c>
       <c r="E5" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F5" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.20454609105863</v>
+        <v>4.583238739797028</v>
       </c>
       <c r="D6" t="n">
-        <v>12.38573547292143</v>
+        <v>2.012682014349732</v>
       </c>
       <c r="E6" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F6" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>9.04879538156181</v>
+        <v>1.470429249503794</v>
       </c>
       <c r="D7" t="n">
-        <v>3.806385865951675</v>
+        <v>0.6185377032171472</v>
       </c>
       <c r="E7" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F7" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.43246422700172</v>
+        <v>3.97027543688778</v>
       </c>
       <c r="D8" t="n">
-        <v>28.68057872367021</v>
+        <v>4.66059404259641</v>
       </c>
       <c r="E8" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F8" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.18953021239189</v>
+        <v>4.905798659513682</v>
       </c>
       <c r="D9" t="n">
-        <v>36.40416616029884</v>
+        <v>5.915677001048562</v>
       </c>
       <c r="E9" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F9" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.24488351572533</v>
+        <v>5.239793571305366</v>
       </c>
       <c r="D10" t="n">
-        <v>15.61738817600588</v>
+        <v>2.537825578600956</v>
       </c>
       <c r="E10" t="n">
-        <v>10.02720559045661</v>
+        <v>1.629420908449199</v>
       </c>
       <c r="F10" t="n">
-        <v>10.0593061913467</v>
+        <v>1.634637256093839</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
